--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="265">
   <si>
     <t>Property</t>
   </si>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Observation</t>
+    <t>element:Observation.bodySite</t>
   </si>
   <si>
     <t>ID</t>
@@ -568,6 +568,262 @@
   </si>
   <si>
     <t>Extension.extension:qualifier.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>特定の歯の『歯根』を指定</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalRootBodyStructure_VS</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.system</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalRootBodyStructure_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.version</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.code</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.display</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:root.userSelected</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface</t>
+  </si>
+  <si>
+    <t>surface</t>
+  </si>
+  <si>
+    <t>特定の歯の『歯面』を指定</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSurfaceBodyStructure_VS</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_CS</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.version</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.code</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.display</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].coding:surface.userSelected</t>
+  </si>
+  <si>
+    <t>Extension.extension:qualifier.value[x].text</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
 </sst>
 </file>
@@ -879,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="86.48046875" customWidth="true" bestFit="true"/>
@@ -896,7 +1152,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -907,17 +1163,17 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.46875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="20.5390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6017,10 +6273,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6028,7 +6284,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>85</v>
@@ -6043,24 +6299,22 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -6102,10 +6356,10 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>85</v>
@@ -6117,26 +6371,26 @@
         <v>77</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>117</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -6148,15 +6402,17 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -6193,33 +6449,2141 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC52" s="2"/>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y53" s="2"/>
+      <c r="Z53" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y61" s="2"/>
+      <c r="Z61" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
+      <c r="B71" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AK51" t="s" s="2">
+      <c r="AK71" t="s" s="2">
         <v>111</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="181">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Observation DentalOral BodyStructure Extension</t>
+    <t>JP Core Observation DentalOral BodyStructure IncludedStructure Extension</t>
   </si>
   <si>
     <t>Status</t>
@@ -568,262 +568,6 @@
   </si>
   <si>
     <t>Extension.extension:qualifier.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root</t>
-  </si>
-  <si>
-    <t>root</t>
-  </si>
-  <si>
-    <t>特定の歯の『歯根』を指定</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalRootBodyStructure_VS</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.system</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalRootBodyStructure_CS</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.version</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.code</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.display</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>システムによって定義された表現 / Representation defined by the system</t>
-  </si>
-  <si>
-    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:root.userSelected</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface</t>
-  </si>
-  <si>
-    <t>surface</t>
-  </si>
-  <si>
-    <t>特定の歯の『歯面』を指定</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalSurfaceBodyStructure_VS</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalSurfaceBodyStructure_CS</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.version</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.code</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.display</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].coding:surface.userSelected</t>
-  </si>
-  <si>
-    <t>Extension.extension:qualifier.value[x].text</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK71"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="86.48046875" customWidth="true" bestFit="true"/>
@@ -1152,7 +896,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1163,17 +907,17 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.46875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.5390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2967,7 +2711,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3486,7 +3230,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4005,7 +3749,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4204,11 +3948,11 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>79</v>
@@ -4226,12 +3970,14 @@
         <v>92</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4295,7 +4041,7 @@
         <v>83</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
@@ -4313,10 +4059,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5043,7 +4789,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6273,10 +6019,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6284,7 +6030,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>85</v>
@@ -6299,22 +6045,24 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -6356,10 +6104,10 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>85</v>
@@ -6371,26 +6119,26 @@
         <v>77</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -6402,17 +6150,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -6449,2141 +6195,33 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AC52" s="2"/>
-      <c r="AD52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y53" s="2"/>
-      <c r="Z53" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y61" s="2"/>
-      <c r="Z61" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK71" t="s" s="2">
         <v>111</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
